--- a/src/test/resources/testData/PharmaConnectTestData.xlsx
+++ b/src/test/resources/testData/PharmaConnectTestData.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A59852D9-C965-41C9-9D30-B2451E652B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97F9A997-114C-41CB-8B1B-9B1646D2C916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
+    <sheet name="RegisterData" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="80">
   <si>
     <t>Role</t>
   </si>
@@ -106,6 +107,174 @@
   </si>
   <si>
     <t>qwewewq</t>
+  </si>
+  <si>
+    <t>TestName</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>FullName(*)</t>
+  </si>
+  <si>
+    <t>Email(*)</t>
+  </si>
+  <si>
+    <t>Phone(*)</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Pincode</t>
+  </si>
+  <si>
+    <t>Password(*)</t>
+  </si>
+  <si>
+    <t>Confirm Password(*)</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Valid User with partial details</t>
+  </si>
+  <si>
+    <t>This is testing valid details lead to search dashboard</t>
+  </si>
+  <si>
+    <t>Automation User</t>
+  </si>
+  <si>
+    <t>generatedDynamically</t>
+  </si>
+  <si>
+    <t>Valid User with all details</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>123, Abc Street, TN</t>
+  </si>
+  <si>
+    <t>Validation for existing email</t>
+  </si>
+  <si>
+    <t>To validate if existing mail is not used again</t>
+  </si>
+  <si>
+    <t>TestAutomation</t>
+  </si>
+  <si>
+    <t>autox@gmail.com</t>
+  </si>
+  <si>
+    <t>An account with this email already exists.</t>
+  </si>
+  <si>
+    <t>Validation for invalid email</t>
+  </si>
+  <si>
+    <t>Providing a Invalid email and checking if it accepts as invalid email</t>
+  </si>
+  <si>
+    <t>Auto</t>
+  </si>
+  <si>
+    <t>auto.com</t>
+  </si>
+  <si>
+    <t>Please enter a valid email address (e.g. john@example.com).</t>
+  </si>
+  <si>
+    <t>Validation for invalid phone number</t>
+  </si>
+  <si>
+    <t>Providing invalid types of phone number to check if it accepts or not</t>
+  </si>
+  <si>
+    <t>Auto1</t>
+  </si>
+  <si>
+    <t>Phone must be exactly 10 digits (e.g. 9876543210).</t>
+  </si>
+  <si>
+    <t>Auto2</t>
+  </si>
+  <si>
+    <t>Auto3</t>
+  </si>
+  <si>
+    <t>asasasasas</t>
+  </si>
+  <si>
+    <t>Validation for existing phone number</t>
+  </si>
+  <si>
+    <t>Providing already existing phone number to validate if it accepts it.</t>
+  </si>
+  <si>
+    <t>Auto4</t>
+  </si>
+  <si>
+    <t>Phone Number Already in Use.</t>
+  </si>
+  <si>
+    <t>Validation for small password</t>
+  </si>
+  <si>
+    <t>Validating if password less than 8 characters is accepted</t>
+  </si>
+  <si>
+    <t>Auto5</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>Password must be at least 8 characters.</t>
+  </si>
+  <si>
+    <t>Validation for confirm password</t>
+  </si>
+  <si>
+    <t>Validating if confirm password and password are working</t>
+  </si>
+  <si>
+    <t>Auto6</t>
+  </si>
+  <si>
+    <t>abcdefgh</t>
+  </si>
+  <si>
+    <t>Passwords do not match.</t>
+  </si>
+  <si>
+    <t>Validation for pincode</t>
+  </si>
+  <si>
+    <t>Validating if pincode is only accepting 6 digits</t>
+  </si>
+  <si>
+    <t>Auto7</t>
+  </si>
+  <si>
+    <t>Pincode must be exactly 6 digits.</t>
+  </si>
+  <si>
+    <t>Auto8</t>
+  </si>
+  <si>
+    <t>Auto9</t>
+  </si>
+  <si>
+    <t>abcdef</t>
   </si>
 </sst>
 </file>
@@ -150,9 +319,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -676,4 +848,424 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E714C358-B9B9-4183-B981-A39021BBDAF9}">
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" customWidth="1"/>
+    <col min="4" max="4" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="26" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" customWidth="1"/>
+    <col min="9" max="9" width="12.28515625" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" style="2" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="30.75">
+      <c r="A2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="30.75">
+      <c r="A3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3">
+        <v>600001</v>
+      </c>
+      <c r="I3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="45.75">
+      <c r="A4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="80.25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="60.75">
+      <c r="A6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6">
+        <v>898989898</v>
+      </c>
+      <c r="I6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="60.75">
+      <c r="A7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7">
+        <v>78787878787</v>
+      </c>
+      <c r="I7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="60.75">
+      <c r="A8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="45.75">
+      <c r="A9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9">
+        <v>9898989832</v>
+      </c>
+      <c r="I9" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="45.75">
+      <c r="A10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="45.75">
+      <c r="A11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11">
+        <v>12345678</v>
+      </c>
+      <c r="J11" t="s">
+        <v>71</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="30.75">
+      <c r="A12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12">
+        <v>1234567</v>
+      </c>
+      <c r="I12" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="30.75">
+      <c r="A13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13">
+        <v>12345</v>
+      </c>
+      <c r="I13" t="s">
+        <v>6</v>
+      </c>
+      <c r="J13" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="30.75">
+      <c r="A14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" t="s">
+        <v>79</v>
+      </c>
+      <c r="I14" t="s">
+        <v>6</v>
+      </c>
+      <c r="J14" t="s">
+        <v>6</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="D15" s="1"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{5083AD58-E1AA-4851-BB0D-AF73B29FC447}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/testData/PharmaConnectTestData.xlsx
+++ b/src/test/resources/testData/PharmaConnectTestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97F9A997-114C-41CB-8B1B-9B1646D2C916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{62403559-CEEF-4473-AFBB-936177CBB899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -852,7 +852,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E714C358-B9B9-4183-B981-A39021BBDAF9}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.85546875" style="2" customWidth="1"/>
@@ -1259,9 +1259,6 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
-      <c r="D15" s="1"/>
-    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D4" r:id="rId1" xr:uid="{5083AD58-E1AA-4851-BB0D-AF73B29FC447}"/>

--- a/src/test/resources/testData/PharmaConnectTestData.xlsx
+++ b/src/test/resources/testData/PharmaConnectTestData.xlsx
@@ -3,13 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{62403559-CEEF-4473-AFBB-936177CBB899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7BD141A1-2D52-41B0-B280-1823CA88770C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
-    <sheet name="RegisterData" sheetId="2" r:id="rId2"/>
+    <sheet name="RegisterPharmacyData" sheetId="3" r:id="rId2"/>
+    <sheet name="RegisterData" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -35,7 +36,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="194">
+  <si>
+    <t>Test Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
   <si>
     <t>Role</t>
   </si>
@@ -49,6 +56,12 @@
     <t>Result</t>
   </si>
   <si>
+    <t>Valid Login Test (Admin)</t>
+  </si>
+  <si>
+    <t>The test is providing valid test data and validating if it is redirected to admin page</t>
+  </si>
+  <si>
     <t>admin</t>
   </si>
   <si>
@@ -61,21 +74,45 @@
     <t>/admin/sellers</t>
   </si>
   <si>
+    <t>Invalid password (Admin)</t>
+  </si>
+  <si>
+    <t>The test is providing invalid test data and validating the error message</t>
+  </si>
+  <si>
     <t>passwrdsdsd</t>
   </si>
   <si>
     <t>Invalid credentials. Please try again.</t>
   </si>
   <si>
+    <t>Invalid Email (Admin)</t>
+  </si>
+  <si>
+    <t>The test is providing invalid email  to check does not allow for admin login</t>
+  </si>
+  <si>
     <t>admin123@pharmaxconnect.com</t>
   </si>
   <si>
     <t>Authentication failed: User not found.</t>
   </si>
   <si>
+    <t>Invalid Email and Password (Admin)</t>
+  </si>
+  <si>
+    <t>The test is providing invalid email and password to check does not allow for admin login</t>
+  </si>
+  <si>
     <t>nasdosadon</t>
   </si>
   <si>
+    <t>Valid Login Test (User)</t>
+  </si>
+  <si>
+    <t>The test is providing valid test data and validating if it is redirected to user page</t>
+  </si>
+  <si>
     <t>user</t>
   </si>
   <si>
@@ -85,12 +122,27 @@
     <t>/search</t>
   </si>
   <si>
+    <t>Invalid password (User)</t>
+  </si>
+  <si>
     <t>pass78987</t>
   </si>
   <si>
+    <t>Invalid Email (User)</t>
+  </si>
+  <si>
     <t>kjhsakjd@gmail.com</t>
   </si>
   <si>
+    <t>Invalid Email and Password (User)</t>
+  </si>
+  <si>
+    <t>Valid Login Test (Pharmacy)</t>
+  </si>
+  <si>
+    <t>The test is providing valid test data and validating if it is redirected to seller page</t>
+  </si>
+  <si>
     <t>pharmacy</t>
   </si>
   <si>
@@ -100,42 +152,366 @@
     <t>/seller/dashboard</t>
   </si>
   <si>
+    <t>Invalid password (Pharmacy)</t>
+  </si>
+  <si>
     <t>sadasdsad</t>
   </si>
   <si>
+    <t>Invalid Email (Pharmacy)</t>
+  </si>
+  <si>
     <t>mnmbm@pc.vom</t>
   </si>
   <si>
+    <t>Invalid Email and Password (Pharmacy)</t>
+  </si>
+  <si>
     <t>qwewewq</t>
   </si>
   <si>
     <t>TestName</t>
   </si>
   <si>
-    <t>Description</t>
+    <t>PharmacyName(*)</t>
+  </si>
+  <si>
+    <t>OwnerName(*)</t>
+  </si>
+  <si>
+    <t>LicenseNumber</t>
+  </si>
+  <si>
+    <t>GSTNumber</t>
+  </si>
+  <si>
+    <t>Email(*)</t>
+  </si>
+  <si>
+    <t>Phone(*)</t>
+  </si>
+  <si>
+    <t>Address(*)</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Pincode</t>
+  </si>
+  <si>
+    <t>OperatingHours</t>
+  </si>
+  <si>
+    <t>Open247</t>
+  </si>
+  <si>
+    <t>Latitude</t>
+  </si>
+  <si>
+    <t>Longitude</t>
+  </si>
+  <si>
+    <t>Password(*)</t>
+  </si>
+  <si>
+    <t>ConfirmPassword(*)</t>
+  </si>
+  <si>
+    <t>ExpectedResult</t>
+  </si>
+  <si>
+    <t>Valid pharmacy with required fields only</t>
+  </si>
+  <si>
+    <t>Register with only required fields and verify redirect to dashboard</t>
+  </si>
+  <si>
+    <t>Apollo Pharmacy</t>
+  </si>
+  <si>
+    <t>Dr. Rajesh Kumar</t>
+  </si>
+  <si>
+    <t> </t>
+  </si>
+  <si>
+    <t>generatedDynamically</t>
+  </si>
+  <si>
+    <t>123 Main Street</t>
+  </si>
+  <si>
+    <t>password123</t>
+  </si>
+  <si>
+    <t>Valid pharmacy with all fields</t>
+  </si>
+  <si>
+    <t>Register with all fields including optional ones and verify redirect</t>
+  </si>
+  <si>
+    <t>PH/2024/123456</t>
+  </si>
+  <si>
+    <t>29ABCDE1234F1Z5</t>
+  </si>
+  <si>
+    <t>Bangalore</t>
+  </si>
+  <si>
+    <t>9 AM - 9 PM</t>
+  </si>
+  <si>
+    <t>Valid pharmacy with 24x7 checked</t>
+  </si>
+  <si>
+    <t>Register with open 24x7 checkbox checked and verify redirect</t>
+  </si>
+  <si>
+    <t>MedPlus Pharmacy</t>
+  </si>
+  <si>
+    <t>Dr. Anita Singh</t>
+  </si>
+  <si>
+    <t>456 Cross Road</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>Valid pharmacy with manual coordinates</t>
+  </si>
+  <si>
+    <t>Register with manually entered latitude and longitude</t>
+  </si>
+  <si>
+    <t>LifeCare Pharmacy</t>
+  </si>
+  <si>
+    <t>Dr. Suresh Rao</t>
+  </si>
+  <si>
+    <t>789 Park Avenue</t>
+  </si>
+  <si>
+    <t>Hyderabad</t>
+  </si>
+  <si>
+    <t>Validation for invalid GST number</t>
+  </si>
+  <si>
+    <t>Provide incorrectly formatted GST number and check validation</t>
+  </si>
+  <si>
+    <t>ABCD1234</t>
+  </si>
+  <si>
+    <t>Invalid GST number format</t>
+  </si>
+  <si>
+    <t>Validation for invalid license number</t>
+  </si>
+  <si>
+    <t>Provide short/invalid license number and check validation</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>Invalid license number</t>
+  </si>
+  <si>
+    <t>Validation for invalid email missing @</t>
+  </si>
+  <si>
+    <t>Provide email without @ symbol and check for invalid email error</t>
+  </si>
+  <si>
+    <t>contact.com</t>
+  </si>
+  <si>
+    <t>Please enter a valid email address (e.g. contact@pharmacy.com)</t>
+  </si>
+  <si>
+    <t>Validation for invalid email missing TLD</t>
+  </si>
+  <si>
+    <t>Provide email without TLD and check for invalid email error</t>
+  </si>
+  <si>
+    <t>contact@pharmacy</t>
+  </si>
+  <si>
+    <t>Validation for invalid email missing domain</t>
+  </si>
+  <si>
+    <t>Provide email with @ but no domain and check for invalid email error</t>
+  </si>
+  <si>
+    <t>contact@</t>
+  </si>
+  <si>
+    <t>Validation for already registered email</t>
+  </si>
+  <si>
+    <t>Use an already registered email and check for duplicate email error</t>
+  </si>
+  <si>
+    <t>existing@pharmacy.com</t>
+  </si>
+  <si>
+    <t>An account with this email already exists.</t>
+  </si>
+  <si>
+    <t>Validation for phone less than 10 digits</t>
+  </si>
+  <si>
+    <t>Provide 9 digit phone number and check for length validation error</t>
+  </si>
+  <si>
+    <t>Phone must be exactly 10 digits (e.g. 9876543210).</t>
+  </si>
+  <si>
+    <t>Validation for phone more than 10 digits</t>
+  </si>
+  <si>
+    <t>Provide 11 digit phone number and check for length validation error</t>
+  </si>
+  <si>
+    <t>Validation for alphabetic phone number</t>
+  </si>
+  <si>
+    <t>Provide alphabetic characters as phone number and check validation</t>
+  </si>
+  <si>
+    <t>asasasasas</t>
+  </si>
+  <si>
+    <t>Validation for already registered phone</t>
+  </si>
+  <si>
+    <t>Provide already registered phone number and check for duplicate error</t>
+  </si>
+  <si>
+    <t>Phone Number Already in Use.</t>
+  </si>
+  <si>
+    <t>Validation for empty address</t>
+  </si>
+  <si>
+    <t>Submit form without address and check for required field error</t>
+  </si>
+  <si>
+    <t>Address is required</t>
+  </si>
+  <si>
+    <t>Validation for pincode more than 6 digits</t>
+  </si>
+  <si>
+    <t>Provide 7 digit pincode and check for length validation error</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>Pincode must be exactly 6 digits.</t>
+  </si>
+  <si>
+    <t>Validation for pincode less than 6 digits</t>
+  </si>
+  <si>
+    <t>Provide 5 digit pincode and check for length validation error</t>
+  </si>
+  <si>
+    <t>Validation for alphabetic pincode</t>
+  </si>
+  <si>
+    <t>Provide alphabetic characters as pincode and check validation</t>
+  </si>
+  <si>
+    <t>abcdef</t>
+  </si>
+  <si>
+    <t>Validation for invalid latitude</t>
+  </si>
+  <si>
+    <t>Provide out of range latitude value and check for coordinates error</t>
+  </si>
+  <si>
+    <t>Invalid coordinates</t>
+  </si>
+  <si>
+    <t>Validation for invalid longitude</t>
+  </si>
+  <si>
+    <t>Provide out of range longitude value and check for coordinates error</t>
+  </si>
+  <si>
+    <t>Validation for password less than 8 characters</t>
+  </si>
+  <si>
+    <t>Provide password shorter than 8 characters and check validation</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>Password must be at least 8 characters.</t>
+  </si>
+  <si>
+    <t>Validation for mismatched confirm password</t>
+  </si>
+  <si>
+    <t>Provide different values for password and confirm password fields</t>
+  </si>
+  <si>
+    <t>different123</t>
+  </si>
+  <si>
+    <t>Passwords do not match.</t>
+  </si>
+  <si>
+    <t>Validation for uncheck terms checkbox</t>
+  </si>
+  <si>
+    <t>Submit form without accepting terms and check for terms error</t>
+  </si>
+  <si>
+    <t>You must confirm the terms to register.</t>
+  </si>
+  <si>
+    <t>Valid operating hours format</t>
+  </si>
+  <si>
+    <t>Provide valid operating hours and verify it is accepted</t>
+  </si>
+  <si>
+    <t>Verify back to home navigation</t>
+  </si>
+  <si>
+    <t>Click back to home link and verify navigation to home page</t>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>Verify login page navigation</t>
+  </si>
+  <si>
+    <t>Click already registered login link and verify navigation to login page</t>
+  </si>
+  <si>
+    <t>/login</t>
   </si>
   <si>
     <t>FullName(*)</t>
   </si>
   <si>
-    <t>Email(*)</t>
-  </si>
-  <si>
-    <t>Phone(*)</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
     <t>Address</t>
   </si>
   <si>
-    <t>Pincode</t>
-  </si>
-  <si>
-    <t>Password(*)</t>
-  </si>
-  <si>
     <t>Confirm Password(*)</t>
   </si>
   <si>
@@ -151,15 +527,9 @@
     <t>Automation User</t>
   </si>
   <si>
-    <t>generatedDynamically</t>
-  </si>
-  <si>
     <t>Valid User with all details</t>
   </si>
   <si>
-    <t>Chennai</t>
-  </si>
-  <si>
     <t>123, Abc Street, TN</t>
   </si>
   <si>
@@ -175,9 +545,6 @@
     <t>autox@gmail.com</t>
   </si>
   <si>
-    <t>An account with this email already exists.</t>
-  </si>
-  <si>
     <t>Validation for invalid email</t>
   </si>
   <si>
@@ -202,18 +569,12 @@
     <t>Auto1</t>
   </si>
   <si>
-    <t>Phone must be exactly 10 digits (e.g. 9876543210).</t>
-  </si>
-  <si>
     <t>Auto2</t>
   </si>
   <si>
     <t>Auto3</t>
   </si>
   <si>
-    <t>asasasasas</t>
-  </si>
-  <si>
     <t>Validation for existing phone number</t>
   </si>
   <si>
@@ -223,9 +584,6 @@
     <t>Auto4</t>
   </si>
   <si>
-    <t>Phone Number Already in Use.</t>
-  </si>
-  <si>
     <t>Validation for small password</t>
   </si>
   <si>
@@ -235,12 +593,6 @@
     <t>Auto5</t>
   </si>
   <si>
-    <t>abc</t>
-  </si>
-  <si>
-    <t>Password must be at least 8 characters.</t>
-  </si>
-  <si>
     <t>Validation for confirm password</t>
   </si>
   <si>
@@ -253,9 +605,6 @@
     <t>abcdefgh</t>
   </si>
   <si>
-    <t>Passwords do not match.</t>
-  </si>
-  <si>
     <t>Validation for pincode</t>
   </si>
   <si>
@@ -265,23 +614,17 @@
     <t>Auto7</t>
   </si>
   <si>
-    <t>Pincode must be exactly 6 digits.</t>
-  </si>
-  <si>
     <t>Auto8</t>
   </si>
   <si>
     <t>Auto9</t>
-  </si>
-  <si>
-    <t>abcdef</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -297,16 +640,80 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+        <bgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAD1DC"/>
+        <bgColor rgb="FFEAD1DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D2E9"/>
+        <bgColor rgb="FFD9D2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F3F3"/>
+        <bgColor rgb="FFF3F3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE599"/>
+        <bgColor rgb="FFFFE599"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -314,15 +721,121 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -640,20 +1153,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.5703125" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" customWidth="1"/>
-    <col min="4" max="4" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.5703125" customWidth="1"/>
+    <col min="5" max="5" width="21.28515625" customWidth="1"/>
+    <col min="6" max="6" width="35.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -662,195 +1177,1814 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="76.5">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="60.75">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="60.75">
       <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="76.5">
       <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="60.75">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="60.75">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
+    <row r="8" spans="1:6" ht="76.5">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="76.5">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9">
+        <v>34304340</v>
+      </c>
+      <c r="F9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="60.75">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="60.75">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="60.75">
+      <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9">
-        <v>34304340</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
         <v>19</v>
       </c>
-      <c r="C10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
+    </row>
+    <row r="13" spans="1:6" ht="76.5">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" t="s">
         <v>19</v>
-      </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{7EF1291D-D636-4956-A81D-B5440C4EB9BE}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{2A5629A7-3079-4C66-813C-F92BF6FDBE2F}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{78F47196-B289-4048-A5F6-0B01D96B6207}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{3266C680-E9D4-4115-BA6A-BF1309C45811}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{31E825E0-6BFD-4D3A-B309-0BF74FE20F5D}"/>
-    <hyperlink ref="B7" r:id="rId6" xr:uid="{1E9CF194-A22A-4ED7-8432-DA1F258FEC29}"/>
-    <hyperlink ref="B8" r:id="rId7" xr:uid="{DA17E474-58AA-4B0A-B965-31AEF820E2D8}"/>
-    <hyperlink ref="B9" r:id="rId8" xr:uid="{92D5FEE3-D82F-4180-8549-D621514D8E2C}"/>
-    <hyperlink ref="B10" r:id="rId9" xr:uid="{4E425672-C68B-4A7A-966C-88DF5F0B546A}"/>
-    <hyperlink ref="B11" r:id="rId10" xr:uid="{312FB689-3D9B-462E-A8F5-A197785D97F0}"/>
-    <hyperlink ref="B12" r:id="rId11" xr:uid="{A8CB82CB-1568-4848-9D34-0474CCDA1B49}"/>
-    <hyperlink ref="B13" r:id="rId12" xr:uid="{78417FB3-66F3-4C7B-9AA4-86C7A4048AE7}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{7EF1291D-D636-4956-A81D-B5440C4EB9BE}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{2A5629A7-3079-4C66-813C-F92BF6FDBE2F}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{78F47196-B289-4048-A5F6-0B01D96B6207}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{3266C680-E9D4-4115-BA6A-BF1309C45811}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{31E825E0-6BFD-4D3A-B309-0BF74FE20F5D}"/>
+    <hyperlink ref="D7" r:id="rId6" xr:uid="{1E9CF194-A22A-4ED7-8432-DA1F258FEC29}"/>
+    <hyperlink ref="D8" r:id="rId7" xr:uid="{DA17E474-58AA-4B0A-B965-31AEF820E2D8}"/>
+    <hyperlink ref="D9" r:id="rId8" xr:uid="{92D5FEE3-D82F-4180-8549-D621514D8E2C}"/>
+    <hyperlink ref="D10" r:id="rId9" xr:uid="{4E425672-C68B-4A7A-966C-88DF5F0B546A}"/>
+    <hyperlink ref="D11" r:id="rId10" xr:uid="{312FB689-3D9B-462E-A8F5-A197785D97F0}"/>
+    <hyperlink ref="D12" r:id="rId11" xr:uid="{A8CB82CB-1568-4848-9D34-0474CCDA1B49}"/>
+    <hyperlink ref="D13" r:id="rId12" xr:uid="{78417FB3-66F3-4C7B-9AA4-86C7A4048AE7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{940AA429-D4CB-410C-A8A6-132D3D9A19FE}">
+  <dimension ref="A1:R27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="2" max="2" width="35.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="5" max="5" width="25.42578125" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" customWidth="1"/>
+    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" customWidth="1"/>
+    <col min="18" max="18" width="21.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="36">
+      <c r="A1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="44.25" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="22.5">
+      <c r="A3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" s="6">
+        <v>560001</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="22.5">
+      <c r="A4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="22.5">
+      <c r="A5" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="K5" s="6">
+        <v>500001</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="N5" s="6">
+        <v>17.385000000000002</v>
+      </c>
+      <c r="O5" s="6">
+        <v>78.486699999999999</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="44.25">
+      <c r="A6" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="33">
+      <c r="A7" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="R7" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="87.75">
+      <c r="A8" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="P8" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q8" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="R8" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="87.75">
+      <c r="A9" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="P9" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q9" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="R9" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="87.75">
+      <c r="A10" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O10" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="P10" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q10" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="R10" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="66.75">
+      <c r="A11" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="N11" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O11" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="P11" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q11" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="R11" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="66.75">
+      <c r="A12" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="12">
+        <v>898989898</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="M12" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="O12" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="P12" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q12" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="R12" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="66.75">
+      <c r="A13" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="12">
+        <v>78787878787</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="M13" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="P13" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q13" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="R13" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="66.75">
+      <c r="A14" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="M14" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="O14" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="P14" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q14" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="R14" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="44.25">
+      <c r="A15" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="12">
+        <v>9898989832</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="M15" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="O15" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="P15" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q15" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="R15" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="33">
+      <c r="A16" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="M16" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="N16" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="O16" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="P16" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q16" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="R16" s="14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="44.25">
+      <c r="A17" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="K17" s="14">
+        <v>1234567</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="M17" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="N17" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="O17" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="P17" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q17" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="R17" s="14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="44.25">
+      <c r="A18" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="K18" s="14">
+        <v>12345</v>
+      </c>
+      <c r="L18" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="M18" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="N18" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="O18" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="P18" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q18" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="R18" s="14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="44.25">
+      <c r="A19" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="M19" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="N19" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="O19" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="P19" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q19" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="R19" s="14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="33">
+      <c r="A20" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L20" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="M20" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="N20" s="14">
+        <v>999.99900000000002</v>
+      </c>
+      <c r="O20" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="P20" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q20" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="R20" s="14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="33">
+      <c r="A21" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N21" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="O21" s="16">
+        <v>999.99900000000002</v>
+      </c>
+      <c r="P21" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q21" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="R21" s="16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="22.5">
+      <c r="A22" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N22" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="O22" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="P22" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q22" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="R22" s="16" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="33">
+      <c r="A23" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="O23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="P23" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q23" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="R23" s="16" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="22.5">
+      <c r="A24" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="P24" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q24" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="R24" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="22.5">
+      <c r="A25" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="J25" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="K25" s="18">
+        <v>560001</v>
+      </c>
+      <c r="L25" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="M25" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="N25" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="O25" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="P25" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q25" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="R25" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="22.5">
+      <c r="A26" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="I26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="J26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="L26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="M26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="N26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="O26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="P26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="R26" s="18" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="22.5">
+      <c r="A27" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="I27" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="M27" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="N27" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="O27" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="P27" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q27" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="R27" s="20" t="s">
+        <v>155</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E714C358-B9B9-4183-B981-A39021BBDAF9}">
   <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -870,393 +3004,393 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="E1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="F1" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="G1" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
       <c r="H1" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="I1" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="J1" t="s">
-        <v>33</v>
+        <v>158</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>34</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="30.75">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>36</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>162</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30.75">
       <c r="A3" s="2" t="s">
-        <v>39</v>
+        <v>163</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>36</v>
+        <v>161</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>162</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="G3" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
       <c r="H3">
         <v>600001</v>
       </c>
       <c r="I3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="45.75">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>165</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>167</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="80.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>169</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>171</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>172</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="I5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>51</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="60.75">
       <c r="A6" s="2" t="s">
-        <v>52</v>
+        <v>174</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E6">
         <v>898989898</v>
       </c>
       <c r="I6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="60.75">
       <c r="A7" s="2" t="s">
-        <v>52</v>
+        <v>174</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E7">
         <v>78787878787</v>
       </c>
       <c r="I7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="60.75">
       <c r="A8" s="2" t="s">
-        <v>52</v>
+        <v>174</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>178</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="I8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="45.75">
       <c r="A9" s="2" t="s">
-        <v>59</v>
+        <v>179</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>181</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E9">
         <v>9898989832</v>
       </c>
       <c r="I9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>62</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="45.75">
       <c r="A10" s="2" t="s">
-        <v>63</v>
+        <v>182</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>64</v>
+        <v>183</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>184</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="I10" t="s">
-        <v>66</v>
+        <v>139</v>
       </c>
       <c r="J10" t="s">
-        <v>66</v>
+        <v>139</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>67</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="45.75">
       <c r="A11" s="2" t="s">
-        <v>68</v>
+        <v>185</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>69</v>
+        <v>186</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>187</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="I11">
         <v>12345678</v>
       </c>
       <c r="J11" t="s">
-        <v>71</v>
+        <v>188</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="30.75">
       <c r="A12" s="2" t="s">
-        <v>73</v>
+        <v>189</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>74</v>
+        <v>190</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="H12">
         <v>1234567</v>
       </c>
       <c r="I12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="30.75">
       <c r="A13" s="2" t="s">
-        <v>73</v>
+        <v>189</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>74</v>
+        <v>190</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="H13">
         <v>12345</v>
       </c>
       <c r="I13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="30.75">
       <c r="A14" s="2" t="s">
-        <v>73</v>
+        <v>189</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>74</v>
+        <v>190</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>193</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="H14" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="I14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/testData/PharmaConnectTestData.xlsx
+++ b/src/test/resources/testData/PharmaConnectTestData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7BD141A1-2D52-41B0-B280-1823CA88770C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{991907DF-1752-4389-8A2C-5067DCBD789C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="188">
   <si>
     <t>Test Name</t>
   </si>
@@ -486,24 +486,6 @@
   </si>
   <si>
     <t>Provide valid operating hours and verify it is accepted</t>
-  </si>
-  <si>
-    <t>Verify back to home navigation</t>
-  </si>
-  <si>
-    <t>Click back to home link and verify navigation to home page</t>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>Verify login page navigation</t>
-  </si>
-  <si>
-    <t>Click already registered login link and verify navigation to login page</t>
-  </si>
-  <si>
-    <t>/login</t>
   </si>
   <si>
     <t>FullName(*)</t>
@@ -651,7 +633,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -704,12 +686,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF3F3F3"/>
         <bgColor rgb="FFF3F3F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE599"/>
-        <bgColor rgb="FFFFE599"/>
       </patternFill>
     </fill>
   </fills>
@@ -778,7 +754,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -830,12 +806,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1445,7 +1415,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{940AA429-D4CB-410C-A8A6-132D3D9A19FE}">
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.140625" customWidth="1"/>
@@ -2865,118 +2835,6 @@
       </c>
       <c r="R25" s="18" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="22.5">
-      <c r="A26" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="H26" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="I26" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="J26" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="K26" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="L26" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="M26" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="N26" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="O26" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="P26" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q26" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="R26" s="18" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="22.5">
-      <c r="A27" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="E27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="H27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="I27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="J27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="K27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="L27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="M27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="N27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="O27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="P27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q27" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="R27" s="20" t="s">
-        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -3010,7 +2868,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D1" t="s">
         <v>49</v>
@@ -3022,7 +2880,7 @@
         <v>52</v>
       </c>
       <c r="G1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="H1" t="s">
         <v>53</v>
@@ -3031,21 +2889,21 @@
         <v>58</v>
       </c>
       <c r="J1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="30.75">
       <c r="A2" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D2" t="s">
         <v>66</v>
@@ -3065,13 +2923,13 @@
     </row>
     <row r="3" spans="1:11" ht="30.75">
       <c r="A3" s="2" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D3" t="s">
         <v>66</v>
@@ -3083,7 +2941,7 @@
         <v>125</v>
       </c>
       <c r="G3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="H3">
         <v>600001</v>
@@ -3100,16 +2958,16 @@
     </row>
     <row r="4" spans="1:11" ht="45.75">
       <c r="A4" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C4" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E4" t="s">
         <v>66</v>
@@ -3126,16 +2984,16 @@
     </row>
     <row r="5" spans="1:11" ht="80.25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E5" t="s">
         <v>66</v>
@@ -3147,18 +3005,18 @@
         <v>10</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="60.75">
       <c r="A6" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>66</v>
@@ -3178,13 +3036,13 @@
     </row>
     <row r="7" spans="1:11" ht="60.75">
       <c r="A7" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>66</v>
@@ -3204,13 +3062,13 @@
     </row>
     <row r="8" spans="1:11" ht="60.75">
       <c r="A8" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C8" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>66</v>
@@ -3230,13 +3088,13 @@
     </row>
     <row r="9" spans="1:11" ht="45.75">
       <c r="A9" s="2" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C9" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>66</v>
@@ -3256,13 +3114,13 @@
     </row>
     <row r="10" spans="1:11" ht="45.75">
       <c r="A10" s="2" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C10" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>66</v>
@@ -3282,13 +3140,13 @@
     </row>
     <row r="11" spans="1:11" ht="45.75">
       <c r="A11" s="2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C11" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>66</v>
@@ -3300,7 +3158,7 @@
         <v>12345678</v>
       </c>
       <c r="J11" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>144</v>
@@ -3308,13 +3166,13 @@
     </row>
     <row r="12" spans="1:11" ht="30.75">
       <c r="A12" s="2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C12" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>66</v>
@@ -3337,13 +3195,13 @@
     </row>
     <row r="13" spans="1:11" ht="30.75">
       <c r="A13" s="2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>66</v>
@@ -3366,13 +3224,13 @@
     </row>
     <row r="14" spans="1:11" ht="30.75">
       <c r="A14" s="2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C14" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>66</v>
